--- a/file/用例模版.xlsx
+++ b/file/用例模版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920"/>
+    <workbookView windowWidth="28800" windowHeight="11460"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>CASE  HUB 执行用例导入模板
 1、标题：必填，填写用例的名称；
@@ -47,6 +47,9 @@
     <t>标题*</t>
   </si>
   <si>
+    <t>所属分组</t>
+  </si>
+  <si>
     <t>前置条件</t>
   </si>
   <si>
@@ -69,6 +72,9 @@
   </si>
   <si>
     <t>登录功能测试用例1（勿删）</t>
+  </si>
+  <si>
+    <t>目录A|目录B</t>
   </si>
   <si>
     <t>用户已注册账号1</t>
@@ -88,7 +94,7 @@
     <t>P1</t>
   </si>
   <si>
-    <t>功能</t>
+    <t>功能用例</t>
   </si>
   <si>
     <t>这是第1条测试用例</t>
@@ -1109,13 +1115,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6" outlineLevelRow="2"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6" outlineLevelRow="3"/>
   <cols>
-    <col min="8" max="8" width="95.3839285714286" customWidth="1"/>
+    <col min="1" max="1" width="24.6964285714286" customWidth="1"/>
+    <col min="2" max="3" width="47.4642857142857" customWidth="1"/>
+    <col min="9" max="9" width="95.3839285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="170" customHeight="1" spans="1:8">
+    <row r="1" ht="170" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1126,8 +1134,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1153,46 +1162,84 @@
         <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" ht="106" spans="1:9">
+    <row r="3" ht="106" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="106" spans="1:10">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
+      <c r="F4" t="s">
         <v>15</v>
       </c>
-      <c r="H3" t="s">
+      <c r="G4" t="s">
         <v>16</v>
       </c>
-      <c r="I3" t="s">
+      <c r="H4" t="s">
         <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="I1:I3" numberStoredAsText="1"/>
+    <ignoredError sqref="J1:J3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/file/用例模版.xlsx
+++ b/file/用例模版.xlsx
@@ -448,9 +448,6 @@
       <c r="I2" t="str">
         <v>备注</v>
       </c>
-      <c r="J2" t="str">
-        <v>备注</v>
-      </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">

--- a/file/用例模版.xlsx
+++ b/file/用例模版.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -401,7 +397,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:I3"/>
+  <cols>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" customWidth="1"/>
+    <col min="24" max="24" width="16.6640625" customWidth="1"/>
+    <col min="25" max="25" width="16.6640625" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -437,7 +461,7 @@
         <v>预期结果*</v>
       </c>
       <c r="F2" t="str">
-        <v>标签</v>
+        <v>适用端</v>
       </c>
       <c r="G2" t="str">
         <v>用例等级*</v>
@@ -470,27 +494,13 @@
       <c r="F3" t="str">
         <v>登录模块1</v>
       </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
       <c r="I3" t="str">
         <v>这是第1条测试用例</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="J4" t="str">
-        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>